--- a/site/CodeSystem-KBV-CS-WEST-Preistyp-Code.xlsx
+++ b/site/CodeSystem-KBV-CS-WEST-Preistyp-Code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T16:29:56+02:00</t>
+    <t>2026-08-26T10:20:04+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/CodeSystem-KBV-CS-WEST-Preistyp-Code.xlsx
+++ b/site/CodeSystem-KBV-CS-WEST-Preistyp-Code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T10:20:04+02:00</t>
+    <t>2026-09-28T11:32:53+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/CodeSystem-KBV-CS-WEST-Preistyp-Code.xlsx
+++ b/site/CodeSystem-KBV-CS-WEST-Preistyp-Code.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T11:32:53+02:00</t>
+    <t>2026-10-06T17:56:52+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
